--- a/BA LAB SANJAY.xlsx
+++ b/BA LAB SANJAY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhino\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FA3048-9D13-4C7B-992E-5EABC598B6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AC20C7-508F-4D98-B679-FE4BC113D322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="10" xr2:uid="{0A5E8E82-E379-44C7-9103-21A1C36FE299}"/>
   </bookViews>
@@ -627,7 +627,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -642,31 +642,24 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -678,14 +671,14 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -706,6 +699,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1090,6 +1089,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="2083709424"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -3983,7 +3983,7 @@
                   <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CC6A999-5912-23EE-B951-8BE7A2CD08FD}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3999,26 +3999,15 @@
             </a:prstGeom>
             <a:noFill/>
             <a:ln w="9525">
-              <a:prstDash val="solid"/>
               <a:miter lim="800000"/>
               <a:headEnd/>
-              <a:tailEnd type="none" w="med" len="med"/>
+              <a:tailEnd/>
             </a:ln>
-            <a:effectLst/>
             <a:extLst>
               <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
                 <a14:hiddenFill>
                   <a:noFill/>
                 </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="808080"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
               </a:ext>
             </a:extLst>
           </xdr:spPr>
@@ -4040,12 +4029,14 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Blank"/>
+      <sheetName val="XLSTAT"/>
     </sheetNames>
     <definedNames>
       <definedName name="RunArrowDown"/>
     </definedNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4686,33 +4677,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
       <c r="M1" s="5"/>
     </row>
     <row r="2" spans="2:13">
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
       <c r="M2" s="5"/>
     </row>
     <row r="3" spans="2:13">
@@ -4747,206 +4738,206 @@
     </row>
     <row r="9" spans="2:13" ht="37.950000000000003" customHeight="1"/>
     <row r="10" spans="2:13" ht="15.6" customHeight="1">
-      <c r="B10" s="33"/>
+      <c r="B10" s="30"/>
     </row>
     <row r="13" spans="2:13">
-      <c r="B13" s="9" t="s">
+      <c r="B13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="14" spans="2:13" ht="15" thickBot="1"/>
     <row r="15" spans="2:13">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="H15" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="I15" s="10" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="2:13">
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="13">
         <v>4</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="13">
         <v>0</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="13">
         <v>4</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="16">
         <v>88</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="16">
         <v>96</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="16">
         <v>91</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="16">
         <v>3.5590260840104371</v>
       </c>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="14">
         <v>0</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="14">
         <v>4</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="17">
         <v>86</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="17">
         <v>96</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="17">
         <v>92.5</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="17">
         <v>4.4347115652166904</v>
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="14">
         <v>0</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="14">
         <v>4</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="17">
         <v>86</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="17">
         <v>95</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="17">
         <v>90.5</v>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="17">
         <v>3.872983346207417</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="15" thickBot="1">
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="15">
         <v>4</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="15">
         <v>0</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="15">
         <v>4</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="18">
         <v>89</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="18">
         <v>97</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="18">
         <v>94</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="18">
         <v>3.4641016151377544</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="9" t="s">
+      <c r="B24" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="15" thickBot="1"/>
     <row r="26" spans="2:9">
-      <c r="B26" s="22"/>
-      <c r="C26" s="23" t="s">
+      <c r="B26" s="19"/>
+      <c r="C26" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="23">
         <v>2.1851912817955679</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="23">
         <v>1.2394711367991564</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="23">
         <v>0.5753375814052768</v>
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="24">
         <v>54.62978204488919</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="24">
         <v>30.986778419978904</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="24">
         <v>14.383439535131917</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" thickBot="1">
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="25">
         <v>54.62978204488919</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="25">
         <v>85.616560464868087</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="25">
         <v>100</v>
       </c>
     </row>
@@ -4956,451 +4947,451 @@
       </c>
     </row>
     <row r="52" spans="2:7">
-      <c r="B52" s="9" t="s">
+      <c r="B52" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="15" thickBot="1"/>
     <row r="54" spans="2:7">
-      <c r="B54" s="22"/>
-      <c r="C54" s="23" t="s">
+      <c r="B54" s="19"/>
+      <c r="C54" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="23" t="s">
+      <c r="D54" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E54" s="23" t="s">
+      <c r="E54" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="55" spans="2:7">
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C55" s="26">
+      <c r="C55" s="23">
         <v>0.4026932777640036</v>
       </c>
-      <c r="D55" s="26">
+      <c r="D55" s="23">
         <v>-0.55394744738427115</v>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="23">
         <v>0.67906362618215854</v>
       </c>
     </row>
     <row r="56" spans="2:7">
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="24">
         <v>0.59391114448164173</v>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="24">
         <v>0.4002852582231336</v>
       </c>
-      <c r="E56" s="27">
+      <c r="E56" s="24">
         <v>0.23068969439049861</v>
       </c>
     </row>
     <row r="57" spans="2:7">
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="24">
         <v>-0.35279175364364124</v>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="24">
         <v>0.63983521018156464</v>
       </c>
-      <c r="E57" s="27">
+      <c r="E57" s="24">
         <v>0.61921587038581571</v>
       </c>
     </row>
     <row r="58" spans="2:7" ht="15" thickBot="1">
-      <c r="B58" s="25" t="s">
+      <c r="B58" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C58" s="28">
+      <c r="C58" s="25">
         <v>0.60053780485930686</v>
       </c>
-      <c r="D58" s="28">
+      <c r="D58" s="25">
         <v>0.35146100978288086</v>
       </c>
-      <c r="E58" s="28">
+      <c r="E58" s="25">
         <v>-0.31972888884286416</v>
       </c>
     </row>
     <row r="61" spans="2:7">
-      <c r="B61" s="9" t="s">
+      <c r="B61" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="15" thickBot="1"/>
     <row r="63" spans="2:7">
-      <c r="B63" s="22"/>
-      <c r="C63" s="23" t="s">
+      <c r="B63" s="19"/>
+      <c r="C63" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D63" s="23" t="s">
+      <c r="D63" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E63" s="23" t="s">
+      <c r="E63" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="64" spans="2:7">
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C64" s="26">
+      <c r="C64" s="23">
         <v>0.59527700911370507</v>
       </c>
-      <c r="D64" s="26">
+      <c r="D64" s="23">
         <v>-0.61671821324653231</v>
       </c>
-      <c r="E64" s="26">
+      <c r="E64" s="23">
         <v>0.51507662330050119</v>
       </c>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="24">
         <v>0.87794276509756042</v>
       </c>
-      <c r="D65" s="27">
+      <c r="D65" s="24">
         <v>0.4456437346285842</v>
       </c>
-      <c r="E65" s="27">
+      <c r="E65" s="24">
         <v>0.17498046462145272</v>
       </c>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="24">
         <v>-0.52151061749791727</v>
       </c>
-      <c r="D66" s="27">
+      <c r="D66" s="24">
         <v>0.71233838057865961</v>
       </c>
-      <c r="E66" s="27">
+      <c r="E66" s="24">
         <v>0.46968149568778444</v>
       </c>
     </row>
     <row r="67" spans="2:5" ht="15" thickBot="1">
-      <c r="B67" s="25" t="s">
+      <c r="B67" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="25">
         <v>0.88773855456773021</v>
       </c>
-      <c r="D67" s="28">
+      <c r="D67" s="25">
         <v>0.39128694789121399</v>
       </c>
-      <c r="E67" s="28">
+      <c r="E67" s="25">
         <v>-0.24251759347308513</v>
       </c>
     </row>
     <row r="70" spans="2:5">
-      <c r="B70" s="9" t="s">
+      <c r="B70" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="71" spans="2:5" ht="15" thickBot="1"/>
     <row r="72" spans="2:5">
-      <c r="B72" s="22"/>
-      <c r="C72" s="23" t="s">
+      <c r="B72" s="19"/>
+      <c r="C72" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D72" s="23" t="s">
+      <c r="D72" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E72" s="23" t="s">
+      <c r="E72" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="73" spans="2:5">
-      <c r="B73" s="24" t="s">
+      <c r="B73" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C73" s="26">
+      <c r="C73" s="23">
         <v>0.59527700911370507</v>
       </c>
-      <c r="D73" s="26">
+      <c r="D73" s="23">
         <v>-0.61671821324653231</v>
       </c>
-      <c r="E73" s="26">
+      <c r="E73" s="23">
         <v>0.51507662330050119</v>
       </c>
     </row>
     <row r="74" spans="2:5">
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="24">
         <v>0.87794276509756042</v>
       </c>
-      <c r="D74" s="27">
+      <c r="D74" s="24">
         <v>0.4456437346285842</v>
       </c>
-      <c r="E74" s="27">
+      <c r="E74" s="24">
         <v>0.17498046462145272</v>
       </c>
     </row>
     <row r="75" spans="2:5">
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="24">
         <v>-0.52151061749791727</v>
       </c>
-      <c r="D75" s="27">
+      <c r="D75" s="24">
         <v>0.71233838057865961</v>
       </c>
-      <c r="E75" s="27">
+      <c r="E75" s="24">
         <v>0.46968149568778444</v>
       </c>
     </row>
     <row r="76" spans="2:5" ht="15" thickBot="1">
-      <c r="B76" s="25" t="s">
+      <c r="B76" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C76" s="28">
+      <c r="C76" s="25">
         <v>0.88773855456773021</v>
       </c>
-      <c r="D76" s="28">
+      <c r="D76" s="25">
         <v>0.39128694789121399</v>
       </c>
-      <c r="E76" s="28">
+      <c r="E76" s="25">
         <v>-0.24251759347308513</v>
       </c>
     </row>
     <row r="79" spans="2:5">
-      <c r="B79" s="9" t="s">
+      <c r="B79" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="2:5" ht="15" thickBot="1"/>
     <row r="81" spans="2:5">
-      <c r="B81" s="22"/>
-      <c r="C81" s="23" t="s">
+      <c r="B81" s="19"/>
+      <c r="C81" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D81" s="23" t="s">
+      <c r="D81" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E81" s="23" t="s">
+      <c r="E81" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="82" spans="2:5">
-      <c r="B82" s="24" t="s">
+      <c r="B82" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C82" s="26">
+      <c r="C82" s="23">
         <v>16.216187595631698</v>
       </c>
-      <c r="D82" s="26">
+      <c r="D82" s="23">
         <v>30.685777446354987</v>
       </c>
-      <c r="E82" s="26">
+      <c r="E82" s="23">
         <v>46.112740840366229</v>
       </c>
     </row>
     <row r="83" spans="2:5">
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="24">
         <v>35.27304475394935</v>
       </c>
-      <c r="D83" s="27">
+      <c r="D83" s="24">
         <v>16.022828795076073</v>
       </c>
-      <c r="E83" s="27">
+      <c r="E83" s="24">
         <v>5.321773509798164</v>
       </c>
     </row>
     <row r="84" spans="2:5">
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="24">
         <v>12.446202143895567</v>
       </c>
-      <c r="D84" s="27">
+      <c r="D84" s="24">
         <v>40.938909618808694</v>
       </c>
-      <c r="E84" s="27">
+      <c r="E84" s="24">
         <v>38.342829413766331</v>
       </c>
     </row>
     <row r="85" spans="2:5" ht="15" thickBot="1">
-      <c r="B85" s="25" t="s">
+      <c r="B85" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C85" s="28">
+      <c r="C85" s="25">
         <v>36.064565506523486</v>
       </c>
-      <c r="D85" s="28">
+      <c r="D85" s="25">
         <v>12.352484139760229</v>
       </c>
-      <c r="E85" s="28">
+      <c r="E85" s="25">
         <v>10.222656236069261</v>
       </c>
     </row>
     <row r="88" spans="2:5">
-      <c r="B88" s="9" t="s">
+      <c r="B88" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="89" spans="2:5" ht="15" thickBot="1"/>
     <row r="90" spans="2:5">
-      <c r="B90" s="22"/>
-      <c r="C90" s="23" t="s">
+      <c r="B90" s="19"/>
+      <c r="C90" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D90" s="23" t="s">
+      <c r="D90" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E90" s="23" t="s">
+      <c r="E90" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="91" spans="2:5">
-      <c r="B91" s="24" t="s">
+      <c r="B91" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C91" s="26">
+      <c r="C91" s="23">
         <v>0.35435471757935816</v>
       </c>
-      <c r="D91" s="29">
+      <c r="D91" s="26">
         <v>0.3803413545499954</v>
       </c>
-      <c r="E91" s="26">
+      <c r="E91" s="23">
         <v>0.26530392787064644</v>
       </c>
     </row>
     <row r="92" spans="2:5">
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C92" s="27">
         <v>0.77078349878714891</v>
       </c>
-      <c r="D92" s="27">
+      <c r="D92" s="24">
         <v>0.19859833821371167</v>
       </c>
-      <c r="E92" s="27">
+      <c r="E92" s="24">
         <v>3.0618162999139421E-2</v>
       </c>
     </row>
     <row r="93" spans="2:5">
-      <c r="B93" s="10" t="s">
+      <c r="B93" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="24">
         <v>0.27197332416305886</v>
       </c>
-      <c r="D93" s="30">
+      <c r="D93" s="27">
         <v>0.50742596844542709</v>
       </c>
-      <c r="E93" s="27">
+      <c r="E93" s="24">
         <v>0.22060070739151416</v>
       </c>
     </row>
     <row r="94" spans="2:5" ht="15" thickBot="1">
-      <c r="B94" s="25" t="s">
+      <c r="B94" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C94" s="31">
+      <c r="C94" s="28">
         <v>0.788079741266002</v>
       </c>
-      <c r="D94" s="28">
+      <c r="D94" s="25">
         <v>0.15310547559002144</v>
       </c>
-      <c r="E94" s="28">
+      <c r="E94" s="25">
         <v>5.8814783143976521E-2</v>
       </c>
     </row>
     <row r="95" spans="2:5">
-      <c r="B95" s="32" t="s">
+      <c r="B95" s="29" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="98" spans="2:5">
-      <c r="B98" s="9" t="s">
+      <c r="B98" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="99" spans="2:5" ht="15" thickBot="1"/>
     <row r="100" spans="2:5">
-      <c r="B100" s="22"/>
-      <c r="C100" s="23" t="s">
+      <c r="B100" s="19"/>
+      <c r="C100" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="23" t="s">
+      <c r="D100" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E100" s="23" t="s">
+      <c r="E100" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="101" spans="2:5">
-      <c r="B101" s="24" t="s">
+      <c r="B101" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C101" s="26">
+      <c r="C101" s="23">
         <v>1.5587157674606946</v>
       </c>
-      <c r="D101" s="26">
+      <c r="D101" s="23">
         <v>-1.4835586606057851</v>
       </c>
-      <c r="E101" s="26">
+      <c r="E101" s="23">
         <v>0.25434482139779613</v>
       </c>
     </row>
     <row r="102" spans="2:5">
-      <c r="B102" s="10" t="s">
+      <c r="B102" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="24">
         <v>-2.4251398997893272</v>
       </c>
-      <c r="D102" s="27">
+      <c r="D102" s="24">
         <v>-0.61764190022634569</v>
       </c>
-      <c r="E102" s="27">
+      <c r="E102" s="24">
         <v>-2.126354985283933E-2</v>
       </c>
     </row>
     <row r="103" spans="2:5">
-      <c r="B103" s="10" t="s">
+      <c r="B103" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="24">
         <v>0.26810397829338883</v>
       </c>
-      <c r="D103" s="27">
+      <c r="D103" s="24">
         <v>1.3403715974941672</v>
       </c>
-      <c r="E103" s="27">
+      <c r="E103" s="24">
         <v>0.93442165168706237</v>
       </c>
     </row>
     <row r="104" spans="2:5" ht="15" thickBot="1">
-      <c r="B104" s="25" t="s">
+      <c r="B104" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C104" s="28">
+      <c r="C104" s="25">
         <v>0.59832015403524419</v>
       </c>
-      <c r="D104" s="28">
+      <c r="D104" s="25">
         <v>0.76082896333796302</v>
       </c>
-      <c r="E104" s="28">
+      <c r="E104" s="25">
         <v>-1.1675029232320191</v>
       </c>
     </row>
@@ -5415,112 +5406,112 @@
       </c>
     </row>
     <row r="150" spans="2:7">
-      <c r="B150" s="9" t="s">
+      <c r="B150" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="151" spans="2:7" ht="15" thickBot="1"/>
     <row r="152" spans="2:7">
-      <c r="B152" s="22"/>
-      <c r="C152" s="23" t="s">
+      <c r="B152" s="19"/>
+      <c r="C152" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D152" s="23" t="s">
+      <c r="D152" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E152" s="23" t="s">
+      <c r="E152" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="153" spans="2:7">
-      <c r="B153" s="24" t="s">
+      <c r="B153" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C153" s="26">
+      <c r="C153" s="23">
         <v>27.79613464472305</v>
       </c>
-      <c r="D153" s="26">
+      <c r="D153" s="23">
         <v>44.392850993332004</v>
       </c>
-      <c r="E153" s="26">
+      <c r="E153" s="23">
         <v>2.8110143619449763</v>
       </c>
     </row>
     <row r="154" spans="2:7">
-      <c r="B154" s="10" t="s">
+      <c r="B154" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C154" s="27">
+      <c r="C154" s="24">
         <v>67.285912022282218</v>
       </c>
-      <c r="D154" s="27">
+      <c r="D154" s="24">
         <v>7.6944413143084409</v>
       </c>
-      <c r="E154" s="27">
+      <c r="E154" s="24">
         <v>1.9646663409324985E-2</v>
       </c>
     </row>
     <row r="155" spans="2:7">
-      <c r="B155" s="10" t="s">
+      <c r="B155" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C155" s="27">
+      <c r="C155" s="24">
         <v>0.82235069963392915</v>
       </c>
-      <c r="D155" s="27">
+      <c r="D155" s="24">
         <v>36.237149176556137</v>
       </c>
-      <c r="E155" s="27">
+      <c r="E155" s="24">
         <v>37.940500123809983</v>
       </c>
     </row>
     <row r="156" spans="2:7" ht="15" thickBot="1">
-      <c r="B156" s="25" t="s">
+      <c r="B156" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C156" s="28">
+      <c r="C156" s="25">
         <v>4.0956026333607856</v>
       </c>
-      <c r="D156" s="28">
+      <c r="D156" s="25">
         <v>11.675558515803459</v>
       </c>
-      <c r="E156" s="28">
+      <c r="E156" s="25">
         <v>59.228838850835771</v>
       </c>
     </row>
     <row r="159" spans="2:7">
-      <c r="B159" s="9" t="s">
+      <c r="B159" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="160" spans="2:7" ht="15" thickBot="1"/>
     <row r="161" spans="2:3">
-      <c r="B161" s="22"/>
-      <c r="C161" s="23" t="s">
+      <c r="B161" s="19"/>
+      <c r="C161" s="20" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="162" spans="2:3">
-      <c r="B162" s="24" t="s">
+      <c r="B162" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="C162" s="26">
+      <c r="C162" s="23">
         <v>0.5</v>
       </c>
     </row>
     <row r="163" spans="2:3">
-      <c r="B163" s="10" t="s">
+      <c r="B163" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C163" s="27">
+      <c r="C163" s="24">
         <v>0.5</v>
       </c>
     </row>
     <row r="164" spans="2:3" ht="15" thickBot="1">
-      <c r="B164" s="25" t="s">
+      <c r="B164" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="C164" s="28">
+      <c r="C164" s="25">
         <v>0.5</v>
       </c>
     </row>
@@ -5530,81 +5521,81 @@
       </c>
     </row>
     <row r="187" spans="2:7">
-      <c r="B187" s="9" t="s">
+      <c r="B187" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="188" spans="2:7" ht="15" thickBot="1"/>
     <row r="189" spans="2:7">
-      <c r="B189" s="22"/>
-      <c r="C189" s="23" t="s">
+      <c r="B189" s="19"/>
+      <c r="C189" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D189" s="23" t="s">
+      <c r="D189" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E189" s="23" t="s">
+      <c r="E189" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="190" spans="2:7">
-      <c r="B190" s="24" t="s">
+      <c r="B190" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C190" s="29">
+      <c r="C190" s="26">
         <v>0.51745997226944018</v>
       </c>
-      <c r="D190" s="26">
+      <c r="D190" s="23">
         <v>0.4687619477062816</v>
       </c>
-      <c r="E190" s="26">
+      <c r="E190" s="23">
         <v>1.3778080024278237E-2</v>
       </c>
     </row>
     <row r="191" spans="2:7">
-      <c r="B191" s="10" t="s">
+      <c r="B191" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C191" s="30">
+      <c r="C191" s="27">
         <v>0.93901976822189404</v>
       </c>
-      <c r="D191" s="27">
+      <c r="D191" s="24">
         <v>6.0908042503023667E-2</v>
       </c>
-      <c r="E191" s="27">
+      <c r="E191" s="24">
         <v>7.2189275082378272E-5</v>
       </c>
     </row>
     <row r="192" spans="2:7">
-      <c r="B192" s="10" t="s">
+      <c r="B192" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C192" s="27">
+      <c r="C192" s="24">
         <v>2.621798573076653E-2</v>
       </c>
-      <c r="D192" s="30">
+      <c r="D192" s="27">
         <v>0.65530463407403006</v>
       </c>
-      <c r="E192" s="27">
+      <c r="E192" s="24">
         <v>0.3184773801952035</v>
       </c>
     </row>
     <row r="193" spans="2:5" ht="15" thickBot="1">
-      <c r="B193" s="25" t="s">
+      <c r="B193" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C193" s="28">
+      <c r="C193" s="25">
         <v>0.15565256168584832</v>
       </c>
-      <c r="D193" s="28">
+      <c r="D193" s="25">
         <v>0.25168833199125118</v>
       </c>
-      <c r="E193" s="31">
+      <c r="E193" s="28">
         <v>0.59265910632290064</v>
       </c>
     </row>
     <row r="194" spans="2:5">
-      <c r="B194" s="32" t="s">
+      <c r="B194" s="29" t="s">
         <v>133</v>
       </c>
     </row>
